--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -643,7 +643,6 @@
           <t>True</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -673,7 +672,6 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>3</t>
@@ -691,7 +689,6 @@
           <t>SIMDATA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>False</t>
@@ -709,7 +706,6 @@
           <t>SCIDATA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>True</t>
@@ -793,7 +789,6 @@
           <t>CREATOR</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pandora MOC</t>
@@ -811,7 +806,6 @@
           <t>CRSOFTV</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>v3.06</t>
@@ -829,7 +823,6 @@
           <t>COMPTYPE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>0</t>
@@ -847,7 +840,6 @@
           <t>TRANSID</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0</t>
@@ -865,7 +857,6 @@
           <t>TARG_ID</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>G1299384497902599936</t>
@@ -883,7 +874,6 @@
           <t>FILENAME</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>2026-07-12__02-42-32.525_VisImg_G1299384497902599936_d1280x1280x0010_b1_e000200000us.sp</t>
@@ -901,7 +891,6 @@
           <t>BINSIZE</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>1</t>
@@ -919,7 +908,6 @@
           <t>BITDEPTH</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>16</t>
@@ -937,7 +925,6 @@
           <t>BITSPIX</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>16</t>
@@ -955,7 +942,6 @@
           <t>ROISTRTX</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>384</t>
@@ -973,7 +959,6 @@
           <t>ROISTRTY</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>384</t>
@@ -991,7 +976,6 @@
           <t>ROISTRTZ</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>0</t>
@@ -1009,7 +993,6 @@
           <t>ROISIZEX</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>1280</t>
@@ -1027,7 +1010,6 @@
           <t>ROISIZEY</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>1280</t>
@@ -1045,7 +1027,6 @@
           <t>ROISIZEZ</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>10</t>
@@ -1063,7 +1044,6 @@
           <t>RICEX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>3</t>
@@ -1081,7 +1061,6 @@
           <t>RICEY</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>11</t>
@@ -1099,7 +1078,6 @@
           <t>CORSTIME</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>837139385</t>
@@ -1117,7 +1095,6 @@
           <t>FINETIME</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>525000000</t>
@@ -1135,7 +1112,6 @@
           <t>CORRMODE</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>0</t>
@@ -1153,7 +1129,6 @@
           <t>EXPTIME</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>200000</t>
@@ -1171,7 +1146,6 @@
           <t>FRMSCLCT</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>10</t>
@@ -1189,7 +1163,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>2nbW3kZT2kbT2kZT</t>
@@ -1207,7 +1180,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>0</t>
@@ -1225,13 +1197,11 @@
           <t>FIXED</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1239,13 +1209,11 @@
           <t>PFSOFTV</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>0.6.0</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1253,13 +1221,11 @@
           <t>PRSOFTV</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>2.9.1</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1267,13 +1233,11 @@
           <t>PFCLASS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>VISDAFFILevel1HDUList</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1281,7 +1245,6 @@
           <t>PFTIME</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>2026-09-09T19:46:13.504</t>
@@ -1401,13 +1364,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1415,13 +1376,11 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1429,13 +1388,11 @@
           <t>NAXIS3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1443,7 +1400,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1461,7 +1417,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1511,7 +1466,6 @@
           <t>32768</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1529,7 +1483,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1537,7 +1490,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>6laA8kY46ka96kY9</t>
@@ -1555,7 +1507,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>4290961373</t>
@@ -1573,13 +1524,11 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>COUNTS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1689,7 +1638,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -1707,7 +1655,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>10</t>
@@ -1725,7 +1672,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1743,7 +1689,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1793,7 +1738,6 @@
           <t>ExposureStartTime_us</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1811,7 +1755,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1829,7 +1772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1847,7 +1789,6 @@
           <t>Temperature</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1865,7 +1806,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1883,7 +1823,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1913,7 +1852,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>lL9poI6olI6olI6o</t>
@@ -1931,7 +1869,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>490153783</t>
@@ -1954,7 +1891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,13 +1988,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2065,7 +2000,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2083,7 +2017,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2101,7 +2034,6 @@
           <t>FRAME</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>JD</t>
@@ -2138,34 +2070,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TIMEPIXR</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1deA4Zc71dcA1Zc7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-09T15:46:13</t>
+          <t>TIME is the middle of each exposure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1deA4Zc71dcA1Zc7</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2634768335</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
@@ -2279,13 +2226,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2293,7 +2238,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2311,7 +2255,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2329,7 +2272,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>second</t>
@@ -2369,7 +2311,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>a9Lad8IVa8Iaa8IU</t>
@@ -2387,7 +2328,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2111832060</t>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -1954,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,28 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:46:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TIMESYS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Time scale</t>
         </is>
       </c>
     </row>
